--- a/output/pdf_financials_xlsx/STMP.xlsx
+++ b/output/pdf_financials_xlsx/STMP.xlsx
@@ -1267,31 +1267,31 @@
         <v>-0.522026</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.973424</v>
+        <v>-0.973424</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.065841</v>
+        <v>-1.065841</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.968838</v>
+        <v>-0.968838</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.959349</v>
+        <v>-0.959349</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>4.803323</v>
+        <v>-4.803323</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.93854</v>
+        <v>-0.93854</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.392076</v>
+        <v>-1.392076</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-4.71298</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.019215</v>
+        <v>-0.019215</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-0.086508</v>
@@ -1567,31 +1567,31 @@
         <v>-0.522026</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.973424</v>
+        <v>-0.973424</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.065841</v>
+        <v>-1.065841</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.968838</v>
+        <v>-0.968838</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.959349</v>
+        <v>-0.959349</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4.803323</v>
+        <v>-4.803323</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.93854</v>
+        <v>-0.93854</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.392076</v>
+        <v>-1.392076</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-4.71298</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.019215</v>
+        <v>-0.019215</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.086508</v>
@@ -1741,31 +1741,31 @@
         <v>-0.522026</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.973424</v>
+        <v>-0.973424</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.065841</v>
+        <v>-1.065841</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.968838</v>
+        <v>-0.968838</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.959349</v>
+        <v>-0.959349</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>4.803323</v>
+        <v>-4.803323</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.93854</v>
+        <v>-0.93854</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.392076</v>
+        <v>-1.392076</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-4.71298</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.019215</v>
+        <v>-0.019215</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-0.086508</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>13.92076</v>
+        <v>-13.92076</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>29.456125</v>
@@ -2035,31 +2035,31 @@
         <v>-0.522026</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.973424</v>
+        <v>-0.973424</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.065841</v>
+        <v>-1.065841</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.968838</v>
+        <v>-0.968838</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.959349</v>
+        <v>-0.959349</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4.803323</v>
+        <v>-4.803323</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.93854</v>
+        <v>-0.93854</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.392076</v>
+        <v>-1.392076</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-4.71298</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.019215</v>
+        <v>-0.019215</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.086508</v>
@@ -2151,31 +2151,31 @@
         <v>-0.522026</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.973424</v>
+        <v>-0.973424</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.065841</v>
+        <v>-1.065841</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.968838</v>
+        <v>-0.968838</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.959349</v>
+        <v>-0.959349</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.803323</v>
+        <v>-4.803323</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.93854</v>
+        <v>-0.93854</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.392076</v>
+        <v>-1.392076</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-4.71298</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.019215</v>
+        <v>-0.019215</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.086508</v>
@@ -2301,31 +2301,31 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -6345,7 +6345,7 @@
         <v>-4.71298</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.019215</v>
+        <v>-0.019215</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-0.086508</v>
@@ -29677,7 +29677,7 @@
         </is>
       </c>
       <c r="O210" s="5" t="n">
-        <v>0.019215</v>
+        <v>-0.019215</v>
       </c>
       <c r="P210" s="5" t="n">
         <v>-0.086508</v>
@@ -42930,7 +42930,7 @@
         <v>-18.204218</v>
       </c>
       <c r="U343" s="5" t="n">
-        <v>0.000266</v>
+        <v>-0.000266</v>
       </c>
     </row>
     <row r="344">
@@ -50168,7 +50168,7 @@
         </is>
       </c>
       <c r="O415" s="5" t="n">
-        <v>0.019215</v>
+        <v>-0.019215</v>
       </c>
       <c r="P415" s="5" t="n">
         <v>-0.086508</v>
@@ -53875,13 +53875,13 @@
         </is>
       </c>
       <c r="L453" s="5" t="n">
-        <v>0.93854</v>
+        <v>-0.93854</v>
       </c>
       <c r="M453" s="5" t="n">
-        <v>1.392076</v>
+        <v>-1.392076</v>
       </c>
       <c r="N453" s="5" t="n">
-        <v>4.71298</v>
+        <v>-4.71298</v>
       </c>
       <c r="O453" t="inlineStr">
         <is>
@@ -54938,19 +54938,19 @@
         </is>
       </c>
       <c r="H464" s="5" t="n">
-        <v>1.065841</v>
+        <v>-1.065841</v>
       </c>
       <c r="I464" s="5" t="n">
-        <v>0.968838</v>
+        <v>-0.968838</v>
       </c>
       <c r="J464" s="5" t="n">
-        <v>0.959349</v>
+        <v>-0.959349</v>
       </c>
       <c r="K464" s="5" t="n">
-        <v>4.803323</v>
+        <v>-4.803323</v>
       </c>
       <c r="L464" s="5" t="n">
-        <v>0.93854</v>
+        <v>-0.93854</v>
       </c>
       <c r="M464" t="inlineStr">
         <is>
@@ -56220,10 +56220,10 @@
         </is>
       </c>
       <c r="G477" s="5" t="n">
-        <v>0.973424</v>
+        <v>-0.973424</v>
       </c>
       <c r="H477" s="5" t="n">
-        <v>1.065841</v>
+        <v>-1.065841</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/STMP.xlsx
+++ b/output/pdf_financials_xlsx/STMP.xlsx
@@ -943,25 +943,25 @@
         <v>0.583955</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.286588</v>
+        <v>0.368766</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.090082</v>
+        <v>0.120347</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.062</v>
+        <v>0.300375</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.219641</v>
+        <v>0.31266</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.203809</v>
+        <v>0.312215</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.017023</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.083895</v>
+        <v>1.605549</v>
       </c>
     </row>
     <row r="11">
@@ -1004,7 +1004,7 @@
         <v>-0.368766</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.090082</v>
+        <v>-0.120347</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-0.300375</v>
@@ -1013,13 +1013,13 @@
         <v>-0.31266</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.203809</v>
+        <v>-0.312215</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.0125</v>
+        <v>-0.017023</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.083895</v>
+        <v>-1.605549</v>
       </c>
     </row>
     <row r="12">
@@ -2452,55 +2452,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.011833</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.034398</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.029541</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.022215</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001316</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.858819</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.030205</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.021744</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.009603</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.018678</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000559</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000383</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.684719</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.513317</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.13675</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.100131</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.6232220000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2568,55 +2568,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.011833</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.034398</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.029541</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.022215</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001316</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.858819</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.030205</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.021744</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.009603</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.018678</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000559</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000383</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.684719</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.513317</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.13675</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.100131</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.6232220000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3264,55 +3264,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.011833</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.046023</v>
+        <v>0.011625</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.040826</v>
+        <v>0.011285</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.023635</v>
+        <v>0.00142</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.005909</v>
+        <v>0.004593</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.862977</v>
+        <v>0.004158</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.030205</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.021744</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.009603</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.031304</v>
+        <v>0.012626</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.000559</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000383</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.684719</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.513317</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.143041</v>
+        <v>0.006291</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.100131</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.296267</v>
+        <v>1.673045</v>
       </c>
     </row>
     <row r="49">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -17943,7 +17943,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -39733,7 +39733,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -39796,16 +39796,16 @@
         <v>0.300375</v>
       </c>
       <c r="R312" s="5" t="n">
-        <v>-0.31266</v>
+        <v>0.31266</v>
       </c>
       <c r="S312" s="5" t="n">
-        <v>-0.312215</v>
+        <v>0.312215</v>
       </c>
       <c r="T312" s="5" t="n">
-        <v>-0.017023</v>
+        <v>0.017023</v>
       </c>
       <c r="U312" s="5" t="n">
-        <v>-1.605549</v>
+        <v>1.605549</v>
       </c>
     </row>
     <row r="313">
@@ -47799,7 +47799,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -47868,10 +47868,10 @@
         </is>
       </c>
       <c r="R392" s="5" t="n">
-        <v>-0.00638</v>
+        <v>0.00638</v>
       </c>
       <c r="S392" s="5" t="n">
-        <v>-0.004431</v>
+        <v>0.004431</v>
       </c>
       <c r="T392" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/STMP.xlsx
+++ b/output/pdf_financials_xlsx/STMP.xlsx
@@ -4308,13 +4308,13 @@
         <v>0</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.1645</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.168834</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.40018</v>
       </c>
     </row>
     <row r="65">
@@ -4479,16 +4479,16 @@
         <v>0</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.01115</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.01049</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.01327</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.087215</v>
       </c>
     </row>
     <row r="68">
@@ -25666,7 +25666,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -27585,7 +27589,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -30128,7 +30136,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
